--- a/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
+++ b/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
@@ -4202,15 +4202,13 @@
       <c r="E5" s="23"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I5" s="23"/>
@@ -4250,11 +4248,7 @@
         </is>
       </c>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -4308,7 +4302,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -4384,17 +4378,9 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="23"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H9" s="21"/>
       <c r="I9" s="23"/>
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
@@ -4465,11 +4451,7 @@
     </row>
     <row r="11" ht="64.69" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -4524,8 +4506,7 @@
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -4599,8 +4580,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="K13" s="23"/>

--- a/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
+++ b/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
@@ -4302,7 +4302,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="E7" s="22"/>

--- a/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
+++ b/sheets/조재수대금교본/검수/Danny Boy (아, 목동아).xlsx
@@ -4038,28 +4038,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="64.69" customHeight="true">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="64.69" customHeight="true">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="64.69" customHeight="true">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="64.69" customHeight="true">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="64.69" customHeight="true">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="64.69" customHeight="true">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="64.69" customHeight="true">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="64.69" customHeight="true">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="64.69" customHeight="true">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="64.69" customHeight="true">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="64.69" customHeight="true">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="64.69" customHeight="true">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="Q14" s="24"/>
     </row>
-    <row r="15" ht="64.69" customHeight="true">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="64.69" customHeight="true">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="64.69" customHeight="true">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4776,7 +4776,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="64.69" customHeight="true">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4805,6 +4805,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>